--- a/financial_models/output/Azalea_Hospice_Operations_Dashboard.xlsx
+++ b/financial_models/output/Azalea_Hospice_Operations_Dashboard.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actuals vs Budget" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Staffing Tracker" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cap &amp; Payroll" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Revenue Model" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Staffing &amp; Payroll" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Operating Budget" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Detailed P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Debt Schedule" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Cash Flow &amp; BS" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Actuals vs Model" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Budget" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Tracker" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cap &amp; Payroll" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing &amp; Payroll" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; BS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Model" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="rhc_tier1">Inputs!$B$5</definedName>
@@ -581,13 +581,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -605,14 +605,14 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -647,8 +647,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -671,13 +671,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -695,14 +695,14 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -737,8 +737,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1448,7 +1448,7 @@
     </comment>
     <comment ref="B110" authorId="0" shapeId="0">
       <text>
-        <t>Sized to fund ramp-period operating need + startup costs. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Sized to pay the seller in full at close + fund startup costs and working-capital reserve. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B111" authorId="0" shapeId="0">
@@ -1463,7 +1463,7 @@
     </comment>
     <comment ref="B113" authorId="0" shapeId="0">
       <text>
-        <t>FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Cash capital contribution by James Bullard (19.5% passive member). FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B114" authorId="0" shapeId="0">
@@ -1821,7 +1821,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -1836,9 +1836,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1858,9 +1858,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="B110" s="9" t="n">
-        <v>500000</v>
+        <v>555000</v>
       </c>
     </row>
     <row r="111">
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="B113" s="9" t="n">
-        <v>250000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="114">
@@ -3994,11 +3994,11 @@
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
         <is>
-          <t>Opening cash = equity + loan - startup - capex</t>
+          <t>Opening cash = equity + loan - startup - capex - license (paid at close)</t>
         </is>
       </c>
       <c r="B139" s="23">
-        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117</f>
+        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117-Inputs!$B$120</f>
         <v/>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Debt Schedule - SBA 7(a) + Hickory license seller note | Combined DSCR shown (target &gt;= 1.25x)</t>
+          <t>Debt Schedule - SBA 7(a) only (seller paid at close) | DSCR shown (target &gt;= 1.25x)</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="B6" s="24">
-        <f>PMT(Inputs!$B$121/12,Inputs!$B$122,-Inputs!$B$120)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>HICKORY LICENSE SELLER NOTE ($300K, 6%, 36 mo)</t>
+          <t>HICKORY LICENSE - PAID AT CLOSE (no seller note; schedule zeroed)</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="C18" s="33">
-        <f>Inputs!$B$120</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="D18" s="24">
@@ -5128,7 +5128,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>COMBINED DEBT SERVICE &amp; COVERAGE</t>
+          <t>DEBT SERVICE &amp; COVERAGE (SBA only)</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>TOTAL DEBT SERVICE (P+I, combined)</t>
+          <t>TOTAL DEBT SERVICE (P+I)</t>
         </is>
       </c>
       <c r="C27" s="23">
@@ -5483,7 +5483,7 @@
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t>COMBINED DSCR (period)</t>
+          <t>DSCR (period)</t>
         </is>
       </c>
       <c r="C29" s="60">
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="B34" s="33">
-        <f>Inputs!$B$120</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="C34" s="33">

--- a/financial_models/output/Azalea_Hospice_Operations_Dashboard.xlsx
+++ b/financial_models/output/Azalea_Hospice_Operations_Dashboard.xlsx
@@ -1448,22 +1448,22 @@
     </comment>
     <comment ref="B110" authorId="0" shapeId="0">
       <text>
-        <t>Sized to pay the seller in full at close + fund startup costs and working-capital reserve. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Sized for startup costs + working-capital reserve (the Hickory acquisition is funded by the bank term loan below). FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B111" authorId="0" shapeId="0">
       <text>
-        <t>FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Typical 7(a) variable: Prime ~7.5% + 3.0% spread. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B112" authorId="0" shapeId="0">
       <text>
-        <t>10-year amortization. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>15-year amortization. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B113" authorId="0" shapeId="0">
       <text>
-        <t>Cash capital contribution by James Bullard (19.5% passive member). FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Cash capital contribution by James Bullard (19.5% passive member); $180K designated as the SBA equity injection. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B114" authorId="0" shapeId="0">
@@ -1498,22 +1498,22 @@
     </comment>
     <comment ref="B120" authorId="0" shapeId="0">
       <text>
-        <t>CHOW: acquire Hickory Hospice's existing Medicare-certified provider number (San Antonio + Tyler alternative-delivery site). Eliminates 855A enrollment gap - Azalea bills from day 1.</t>
+        <t>CHOW: purchase 100% of Hickory Hospice LLC's membership interests; its Medicare-certified provider number conveys with the entity (Azalea bills from day 1). Funded by the bank term loan below.</t>
       </text>
     </comment>
     <comment ref="B121" authorId="0" shapeId="0">
       <text>
-        <t>Seller financing on the license acquisition.</t>
+        <t>Concurrent bank term loan (Jim Bullard's bank); Jim personally guarantees. Subordinate to the SBA loan.</t>
       </text>
     </comment>
     <comment ref="B122" authorId="0" shapeId="0">
       <text>
-        <t>Monthly P+I amortization.</t>
+        <t>3-year monthly P+I amortization.</t>
       </text>
     </comment>
     <comment ref="B123" authorId="0" shapeId="0">
       <text>
-        <t>GAAP intangible amortization - non-cash, below EBITDA. No effect on DSCR.</t>
+        <t>GAAP intangible amortization - non-cash, below EBITDA. No effect on DSCR. Confirm tax treatment of a membership-interest purchase with CPA.</t>
       </text>
     </comment>
     <comment ref="B126" authorId="0" shapeId="0">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="B110" s="9" t="n">
-        <v>555000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="111">
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="B111" s="7" t="n">
-        <v>0.115</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="112">
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="B112" s="17" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="113">
@@ -3842,7 +3842,7 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>Hickory Medicare license - acquisition cost ($)</t>
+          <t>Hickory acquisition - purchase price ($)</t>
         </is>
       </c>
       <c r="B120" s="9" t="n">
@@ -3852,7 +3852,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>License note interest rate (APR)</t>
+          <t>Acquisition bank loan rate (APR)</t>
         </is>
       </c>
       <c r="B121" s="7" t="n">
@@ -3862,7 +3862,7 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>License note term (months)</t>
+          <t>Acquisition bank loan term (months)</t>
         </is>
       </c>
       <c r="B122" s="17" t="n">
@@ -3872,7 +3872,7 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>License intangible amortization life (yrs)</t>
+          <t>Acquisition intangible amortization life (yrs)</t>
         </is>
       </c>
       <c r="B123" s="17" t="n">
@@ -3994,11 +3994,11 @@
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
         <is>
-          <t>Opening cash = equity + loan - startup - capex - license (paid at close)</t>
+          <t>Opening cash = equity + loan - startup - capex</t>
         </is>
       </c>
       <c r="B139" s="23">
-        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117-Inputs!$B$120</f>
+        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117</f>
         <v/>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Debt Schedule - SBA 7(a) only (seller paid at close) | DSCR shown (target &gt;= 1.25x)</t>
+          <t>Debt Schedule - SBA 7(a) + Hickory license seller note | Combined DSCR shown (target &gt;= 1.25x)</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="B6" s="24">
-        <f>0</f>
+        <f>PMT(Inputs!$B$121/12,Inputs!$B$122,-Inputs!$B$120)</f>
         <v/>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>HICKORY LICENSE - PAID AT CLOSE (no seller note; schedule zeroed)</t>
+          <t>HICKORY LICENSE SELLER NOTE ($300K, 6%, 36 mo)</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="C18" s="33">
-        <f>0</f>
+        <f>Inputs!$B$120</f>
         <v/>
       </c>
       <c r="D18" s="24">
@@ -5128,7 +5128,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>DEBT SERVICE &amp; COVERAGE (SBA only)</t>
+          <t>COMBINED DEBT SERVICE &amp; COVERAGE</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>TOTAL DEBT SERVICE (P+I)</t>
+          <t>TOTAL DEBT SERVICE (P+I, combined)</t>
         </is>
       </c>
       <c r="C27" s="23">
@@ -5483,7 +5483,7 @@
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t>DSCR (period)</t>
+          <t>COMBINED DSCR (period)</t>
         </is>
       </c>
       <c r="C29" s="60">
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="B34" s="33">
-        <f>0</f>
+        <f>Inputs!$B$120</f>
         <v/>
       </c>
       <c r="C34" s="33">
